--- a/output/pdf_financials_xlsx/DOCT.xlsx
+++ b/output/pdf_financials_xlsx/DOCT.xlsx
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.305803</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.186443</v>
       </c>
     </row>
     <row r="93">
@@ -2816,7 +2816,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>2.305803</v>
       </c>

--- a/output/pdf_financials_xlsx/DOCT.xlsx
+++ b/output/pdf_financials_xlsx/DOCT.xlsx
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-1.400846</v>
+        <v>-0.835114</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.595964</v>
+        <v>-0.5520040000000001</v>
       </c>
     </row>
     <row r="21">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.565732</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.04396</v>
       </c>
     </row>
     <row r="22">
@@ -1739,15 +1739,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.835114</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.5520040000000001</v>
       </c>
     </row>
     <row r="100">
@@ -1756,15 +1752,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1773,15 +1765,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.012568</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.003192</v>
       </c>
     </row>
     <row r="102">
@@ -1790,15 +1778,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1807,15 +1791,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.013274</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.000905</v>
       </c>
     </row>
     <row r="104">
@@ -1824,15 +1804,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.060399</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.023238</v>
       </c>
     </row>
     <row r="105">
@@ -1841,15 +1817,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1858,15 +1830,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.086241</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.027335</v>
       </c>
     </row>
     <row r="107">
@@ -1875,15 +1843,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.122553</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1892,15 +1856,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1909,15 +1869,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1926,15 +1882,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1943,15 +1895,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1960,15 +1908,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1977,15 +1921,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1994,15 +1934,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2011,15 +1947,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2028,15 +1960,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2045,15 +1973,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2062,15 +1986,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2096,15 +2016,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2113,15 +2029,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2130,15 +2042,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2147,15 +2055,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2164,15 +2068,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2181,15 +2081,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2198,15 +2094,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2232,15 +2124,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2266,15 +2154,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>1.430761</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.536753</v>
       </c>
     </row>
     <row r="131">
@@ -2283,15 +2167,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2300,15 +2180,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.947287</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.497044</v>
       </c>
     </row>
     <row r="133">
@@ -2317,15 +2193,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.536753</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.06414</v>
       </c>
     </row>
     <row r="134">
@@ -2334,15 +2206,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2373,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2939,37 +2807,45 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Operating Activities</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Note December 31, 2023 December</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
-        <v>0.002022</v>
+        <v>-0.835114</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.5520040000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Adjustments for non-cash/non-operating items</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bad debts $</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2985,343 +2861,347 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Adjustments for non-cash/non-operating items</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Business development 8</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>0.11019</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.042</v>
+        <v>0.122553</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Consulting fees 8</t>
+          <t>GST receivables</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.032</v>
+        <v>0.012568</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.066</v>
+        <v>0.003192</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>General office and administrative</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
-        <v>0.005739</v>
+        <v>0.013274</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.001679</v>
+        <v>0.000905</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Management fees 8</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.3225</v>
+        <v>0.060399</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.2837</v>
+        <v>0.023238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Professional fees 8</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Due to related parties</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>0.204277</v>
+        <v>0.006635</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.120663</v>
+        <v>0.02404</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Share-based compensation 8</t>
+          <t>Net cash used in operating activities - continued operations</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>0.122553</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.617668</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.500629</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Net cash (used in) provided by operating activities - discontinued operations</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>0.039665</v>
+        <v>-0.329619</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.034432</v>
+        <v>-0.026415</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>0.838941</v>
+          <t>Proceeds from related party loan payable</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.548474</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0.003827</v>
+          <t>Net cash provided by financing activity- continued operations</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.00353</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Loss from continuing operations 9</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Changes in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
-        <v>-0.835114</v>
+        <v>-0.947287</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.5520040000000001</v>
+        <v>-0.497044</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Loss from discontinued operations 9</t>
+          <t>Change in cash and cash equivalents included in disposal group</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>-0.565732</v>
+        <v>0.053279</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.04396</v>
+        <v>0.024431</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Cash and cash equivalents, beginning of the year</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-1.400846</v>
+        <v>1.430761</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-0.595964</v>
+        <v>0.536753</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>From continuing operations $</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of the year $</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>0.536753</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.06414</v>
       </c>
     </row>
     <row r="36">
@@ -3330,22 +3210,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>From discontinued operations $</t>
+          <t>Note December 31, 2023 December</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.002022</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-1e-08</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="37">
@@ -3356,24 +3232,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Bad debts $</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>7.913975</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>7.913975</v>
+        <v>0.002017</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3384,20 +3258,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 7,913,975 23,577,053 1,078,299 2,137,841</t>
+          <t>Business development 8</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>1.539541</v>
+        <v>0.11019</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-25.253652</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="39">
@@ -3408,22 +3282,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fair value of warrants expired - - - (17,222)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Consulting fees 8</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.032</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.017222</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="40">
@@ -3434,22 +3310,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 122,553 -</t>
+          <t>General office and administrative</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>0.122553</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005739</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.001679</v>
       </c>
     </row>
     <row r="41">
@@ -3460,22 +3334,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fair value of stock options expired - - (1,015,668) -</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees 8</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.3225</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>1.015668</v>
+        <v>0.2837</v>
       </c>
     </row>
     <row r="42">
@@ -3486,24 +3362,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
+          <t>Professional fees 8</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-1.400846</v>
+        <v>0.204277</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-1.400846</v>
+        <v>0.120663</v>
       </c>
     </row>
     <row r="43">
@@ -3514,20 +3390,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 7,913,975 23,577,053 185,184 2,120,619</t>
+          <t>Share-based compensation 8</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.261248</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>-25.621608</v>
+        <v>0.122553</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3538,22 +3416,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fair value of warrants expired - - - (39,221)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.039665</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.039221</v>
+        <v>0.034432</v>
       </c>
     </row>
     <row r="45">
@@ -3564,22 +3444,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fair value of stock options expired - - (80,139) -</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.838941</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.080139</v>
+        <v>0.548474</v>
       </c>
     </row>
     <row r="46">
@@ -3590,19 +3472,413 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unrealized gain (loss) on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.003827</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>-0.00353</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Loss from continuing operations 9</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>-0.835114</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>-0.5520040000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Loss from discontinued operations 9</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-0.565732</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>-0.04396</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-1.400846</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-0.595964</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>From continuing operations $</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" s="5" t="n">
+        <v>-1.1e-07</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>From discontinued operations $</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>7.913975</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>7.913975</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2021 7,913,975 23,577,053 1,078,299 2,137,841</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>1.539541</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-25.253652</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Fair value of warrants expired - - - (17,222)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.017222</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 122,553 -</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>0.122553</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fair value of stock options expired - - (1,015,668) -</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>1.015668</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>-1.400846</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-1.400846</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 7,913,975 23,577,053 185,184 2,120,619</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>0.261248</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>-25.621608</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Fair value of warrants expired - - - (39,221)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.039221</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Fair value of stock options expired - - (80,139) -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.080139</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>shares        Amount          reserve       Warrant reserve         Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>Balance, December 31, 2023 7,913,975 23,577,053 105,045 2,081,398</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" s="5" t="n">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
         <v>-0.334716</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F61" s="5" t="n">
         <v>-26.098212</v>
       </c>
     </row>
